--- a/DocumentUnderstandingProcess/contentFiles/any/any/pt0/VisualBasic/Tests/Cache/Config_Expected.xlsx
+++ b/DocumentUnderstandingProcess/contentFiles/any/any/pt0/VisualBasic/Tests/Cache/Config_Expected.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teodora.patrascu\PycharmProjects\Develop\DocumentUnderstandingProcess\contentFiles\any\any\pt0\VisualBasic\Tests\Cache\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teodora.patrascu\PycharmProjects\Cross_platform\DocumentUnderstandingProcess\contentFiles\any\any\pt0\VisualBasic\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5909AC27-75BB-41D9-B027-5B3DECEDB349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0DF345-8765-405C-AFF6-B1BB63538D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21252" yWindow="-17568" windowWidth="30936" windowHeight="17040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="274">
   <si>
     <t>Name</t>
   </si>
@@ -782,9 +782,6 @@
     <t>AutocorrectStorageBucketDirectoryPath</t>
   </si>
   <si>
-    <t>AutocorrectionLearningFile</t>
-  </si>
-  <si>
     <t>Path inside the Storage Bucket where the autocorrect file is stored. Has a corresponding asset that can be configured to overwrite this setting.</t>
   </si>
   <si>
@@ -800,12 +797,6 @@
     <t>A flag that determines if autocorrection should be called or not. Has a corresponding asset that can be configured to overwrite this setting.</t>
   </si>
   <si>
-    <t>AutocorrectionFieldName</t>
-  </si>
-  <si>
-    <t>The name of the field we want to enable autocorrection for. Has a corresponding asset that can be configured to overwrite this setting.</t>
-  </si>
-  <si>
     <t>DU_AutocorrectStorageBucketDirectoryPath</t>
   </si>
   <si>
@@ -824,12 +815,6 @@
     <t>A flag that determines if autocorrection should be called or not. The asset value overrides the one from the "AutocorrectOcrMistakes" sheet</t>
   </si>
   <si>
-    <t>DU_AutocorrectionFieldName</t>
-  </si>
-  <si>
-    <t>The name of the field we want to enable autocorrection for. The asset value overrides the one from the "AutocorrectOcrMistakes" sheet</t>
-  </si>
-  <si>
     <t>LogMessage_AutocorrectOcrMistakesStart</t>
   </si>
   <si>
@@ -851,7 +836,28 @@
     <t>RetryIntervalLow</t>
   </si>
   <si>
-    <t>Tax Amount,Net Amount,Discount,Shipping Charges,Billing Name,Total, Name, Vendor Address, Billing Address, Billing VAT Number, Payment Address, Vendor VAT Number, DueDate,Payment Terms,Discount</t>
+    <t>AutocorrectionLearningFile.json</t>
+  </si>
+  <si>
+    <t>AutocorrectionFieldIdList</t>
+  </si>
+  <si>
+    <t>A comma separated list of the taxonomy ids of the fields we want to enable autocorrection for. Has a corresponding asset that can be configured to overwrite this setting.</t>
+  </si>
+  <si>
+    <t>DU_AutocorrectionFieldIdList</t>
+  </si>
+  <si>
+    <t>DU_DateFormats</t>
+  </si>
+  <si>
+    <t>Different date formats.</t>
+  </si>
+  <si>
+    <t>yyyy-MM-dd;dd-MM-yyyy;MM-dd-yyyy;MM/dd/yyyy;dd/MM/yyyy;yyyy/MM/dd;dd.MM.yyyy;MM.dd.yyyy;yyyy.MM.dd</t>
+  </si>
+  <si>
+    <t>Tax Amount,Net Amount,Discount,Shipping Charges,Billing Name,Total, Name, Vendor Address, Billing Address, Billing VAT Number, Payment Address, Vendor VAT Number, DueDate,Payment Terms</t>
   </si>
 </sst>
 </file>
@@ -1249,7 +1255,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1006"/>
+  <dimension ref="A1:Z1007"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.88671875" customWidth="1"/>
@@ -1433,138 +1439,150 @@
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>162</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>178</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>184</v>
-      </c>
+      <c r="A20" s="2"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="2"/>
+      <c r="A21" t="s">
+        <v>209</v>
+      </c>
+      <c r="B21">
+        <v>0.5</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>209</v>
-      </c>
-      <c r="B22">
-        <v>0.5</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>210</v>
-      </c>
+      <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="2"/>
+      <c r="A23" t="s">
+        <v>238</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C23" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>238</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C24" t="s">
-        <v>240</v>
-      </c>
+      <c r="B24" s="2"/>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="2"/>
+      <c r="A25" t="s">
+        <v>270</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C25" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>35</v>
-      </c>
       <c r="B26" s="2"/>
-      <c r="C26" t="s">
-        <v>203</v>
-      </c>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>36</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B27" s="2"/>
       <c r="C27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="2"/>
+        <v>36</v>
+      </c>
       <c r="C28" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>114</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B29" s="2"/>
       <c r="C29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>78</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>245</v>
+        <v>114</v>
       </c>
       <c r="C30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C31" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>79</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C32" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2538,6 +2556,7 @@
     <row r="1004" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1005" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1006" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1007" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2636,13 +2655,13 @@
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B7">
         <v>99999</v>
       </c>
       <c r="C7" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2669,7 +2688,7 @@
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -2866,18 +2885,18 @@
     </row>
     <row r="36" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B36" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B37" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4220,47 +4239,57 @@
         <v>247</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D16" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B17" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D17" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B18" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D18" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B19" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D19" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>270</v>
+      </c>
+      <c r="B21" t="s">
+        <v>270</v>
+      </c>
+      <c r="D21" t="s">
+        <v>271</v>
+      </c>
+    </row>
     <row r="22" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -5397,7 +5426,7 @@
         <v>151</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C19" t="s">
         <v>152</v>
@@ -5689,41 +5718,41 @@
         <v>247</v>
       </c>
       <c r="B3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C3" t="s">
         <v>248</v>
-      </c>
-      <c r="C3" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
         <v>250</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B6" t="b">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="C7" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
